--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1727,10 +1727,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118256333</v>
+        <v>118257350</v>
       </c>
       <c r="B10" t="n">
-        <v>91124</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1739,40 +1739,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1781,13 +1781,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588772</v>
+        <v>589031</v>
       </c>
       <c r="R10" t="n">
-        <v>6633984</v>
+        <v>6634135</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1838,24 +1838,19 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Död ved  vedartad växt</t>
+          <t>Mark/jord på land</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead wood # Picea abies</t>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1873,7 +1868,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118257350</v>
+        <v>118259347</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1908,7 +1903,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1927,13 +1922,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589031</v>
+        <v>588636</v>
       </c>
       <c r="R11" t="n">
-        <v>6634135</v>
+        <v>6634161</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1962,7 +1957,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1972,7 +1967,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2014,7 +2009,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118259347</v>
+        <v>118255974</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -2047,34 +2042,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerins (Västerins), Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588636</v>
+        <v>588619</v>
       </c>
       <c r="R12" t="n">
-        <v>6634161</v>
+        <v>6634070</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2103,7 +2084,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2113,7 +2094,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2124,41 +2105,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118255974</v>
+        <v>118256333</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>91124</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2167,41 +2133,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerins (Västerins), Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588619</v>
+        <v>588772</v>
       </c>
       <c r="R13" t="n">
-        <v>6634070</v>
+        <v>6633984</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2230,7 +2210,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2240,7 +2220,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2251,16 +2231,36 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1449,10 +1449,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118255310</v>
+        <v>118260266</v>
       </c>
       <c r="B8" t="n">
-        <v>104940</v>
+        <v>57306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1461,55 +1461,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västerins (Västerins), Vstm</t>
+          <t>Överstmossen (Överstmossen), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588600</v>
+        <v>588555</v>
       </c>
       <c r="R8" t="n">
-        <v>6634013</v>
+        <v>6634111</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1538,7 +1524,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1548,7 +1534,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,14 +1551,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Mark/jord på land</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Ground/soil on land</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1590,10 +1586,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118260266</v>
+        <v>118255310</v>
       </c>
       <c r="B9" t="n">
-        <v>57306</v>
+        <v>104940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1602,41 +1598,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Överstmossen (Överstmossen), Vstm</t>
+          <t>Västerins (Västerins), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588555</v>
+        <v>588600</v>
       </c>
       <c r="R9" t="n">
-        <v>6634111</v>
+        <v>6634013</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1665,7 +1675,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1675,7 +1685,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1692,24 +1702,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Mark/jord på land</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Ground/soil on land</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118257350</v>
+        <v>118256333</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>91124</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1739,40 +1739,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1781,13 +1781,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589031</v>
+        <v>588772</v>
       </c>
       <c r="R10" t="n">
-        <v>6634135</v>
+        <v>6633984</v>
       </c>
       <c r="S10" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1838,19 +1838,24 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Mark/jord på land</t>
+          <t>Död ved  vedartad växt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Ground/soil on land</t>
+          <t>Dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1868,7 +1873,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118259347</v>
+        <v>118257350</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1903,7 +1908,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1922,13 +1927,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588636</v>
+        <v>589031</v>
       </c>
       <c r="R11" t="n">
-        <v>6634161</v>
+        <v>6634135</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1957,7 +1962,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1967,7 +1972,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2009,7 +2014,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118255974</v>
+        <v>118259347</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -2042,20 +2047,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerins (Västerins), Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588619</v>
+        <v>588636</v>
       </c>
       <c r="R12" t="n">
-        <v>6634070</v>
+        <v>6634161</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2084,7 +2103,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2094,7 +2113,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2105,26 +2124,41 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118256333</v>
+        <v>118255974</v>
       </c>
       <c r="B13" t="n">
-        <v>91124</v>
+        <v>97846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2133,55 +2167,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerins (Västerins), Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588772</v>
+        <v>588619</v>
       </c>
       <c r="R13" t="n">
-        <v>6633984</v>
+        <v>6634070</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2210,7 +2230,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2220,7 +2240,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2231,36 +2251,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118257612</v>
+        <v>118256333</v>
       </c>
       <c r="B4" t="n">
-        <v>104940</v>
+        <v>91124</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,36 +935,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,13 +973,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589000</v>
+        <v>588772</v>
       </c>
       <c r="R4" t="n">
-        <v>6634236</v>
+        <v>6633984</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,19 +1030,24 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Mark/jord på land</t>
+          <t>Död ved  vedartad växt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Ground/soil on land</t>
+          <t>Dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118257576</v>
+        <v>118257613</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,30 +1077,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1105,7 +1110,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,13 +1119,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589005</v>
+        <v>589043</v>
       </c>
       <c r="R5" t="n">
-        <v>6634232</v>
+        <v>6634245</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1149,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,41 +1175,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118256669</v>
+        <v>118257576</v>
       </c>
       <c r="B6" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,41 +1203,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västerins (Västerins), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588825</v>
+        <v>589005</v>
       </c>
       <c r="R6" t="n">
-        <v>6634065</v>
+        <v>6634232</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1286,7 +1290,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,26 +1301,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118255830</v>
+        <v>118259347</v>
       </c>
       <c r="B7" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1325,30 +1344,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1362,13 +1386,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588599</v>
+        <v>588636</v>
       </c>
       <c r="R7" t="n">
-        <v>6634022</v>
+        <v>6634161</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1397,7 +1421,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1407,7 +1431,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,10 +1473,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118260266</v>
+        <v>118254060</v>
       </c>
       <c r="B8" t="n">
-        <v>57306</v>
+        <v>104940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1461,25 +1485,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1489,13 +1513,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588555</v>
+        <v>588352</v>
       </c>
       <c r="R8" t="n">
-        <v>6634111</v>
+        <v>6634031</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1524,7 +1548,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1534,7 +1558,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,48 +1569,23 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118255310</v>
+        <v>118255830</v>
       </c>
       <c r="B9" t="n">
         <v>104940</v>
@@ -1621,12 +1620,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1640,10 +1634,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588600</v>
+        <v>588599</v>
       </c>
       <c r="R9" t="n">
-        <v>6634013</v>
+        <v>6634022</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1675,7 +1669,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1685,7 +1679,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1727,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118256333</v>
+        <v>118260266</v>
       </c>
       <c r="B10" t="n">
-        <v>91124</v>
+        <v>57306</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1739,55 +1733,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västerins (Västerins), Vstm</t>
+          <t>Överstmossen (Överstmossen), Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588772</v>
+        <v>588555</v>
       </c>
       <c r="R10" t="n">
-        <v>6633984</v>
+        <v>6634111</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1816,7 +1796,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1826,7 +1806,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1838,24 +1818,29 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Död ved  vedartad växt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead wood # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1873,10 +1858,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118257350</v>
+        <v>118257140</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1885,30 +1870,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1918,7 +1903,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1927,13 +1912,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589031</v>
+        <v>588991</v>
       </c>
       <c r="R11" t="n">
-        <v>6634135</v>
+        <v>6634058</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1962,7 +1947,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1972,7 +1957,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2014,7 +1999,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118259347</v>
+        <v>118257350</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -2049,7 +2034,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2068,13 +2053,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588636</v>
+        <v>589031</v>
       </c>
       <c r="R12" t="n">
-        <v>6634161</v>
+        <v>6634135</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2103,7 +2088,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2113,7 +2098,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2155,10 +2140,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118255974</v>
+        <v>118257612</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2167,41 +2152,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerins (Västerins), Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588619</v>
+        <v>589000</v>
       </c>
       <c r="R13" t="n">
-        <v>6634070</v>
+        <v>6634236</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2230,7 +2229,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2240,7 +2239,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2251,23 +2250,38 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118254060</v>
+        <v>118255310</v>
       </c>
       <c r="B14" t="n">
         <v>104940</v>
@@ -2300,20 +2314,34 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Överstmossen (Överstmossen), Vstm</t>
+          <t>Västerins (Västerins), Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588352</v>
+        <v>588600</v>
       </c>
       <c r="R14" t="n">
-        <v>6634031</v>
+        <v>6634013</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2342,7 +2370,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2352,7 +2380,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2363,26 +2391,41 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Mark/jord på land</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Ground/soil on land</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118257613</v>
+        <v>118255974</v>
       </c>
       <c r="B15" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2391,55 +2434,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerins (Västerins), Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589043</v>
+        <v>588619</v>
       </c>
       <c r="R15" t="n">
-        <v>6634245</v>
+        <v>6634070</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2468,7 +2497,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2478,7 +2507,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2505,7 +2534,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118257140</v>
+        <v>118256669</v>
       </c>
       <c r="B16" t="n">
         <v>104940</v>
@@ -2538,31 +2567,17 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västerins (Västerins), Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588991</v>
+        <v>588825</v>
       </c>
       <c r="R16" t="n">
-        <v>6634058</v>
+        <v>6634065</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2594,7 +2609,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2604,7 +2619,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2615,31 +2630,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Mark/jord på land</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Ground/soil on land</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118253803</v>
+        <v>118271746</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3061,24 +3061,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Överstmossen (Överstmossen), Vstm</t>
+          <t>Kivsta, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588370</v>
+        <v>588381</v>
       </c>
       <c r="R20" t="n">
-        <v>6634068</v>
+        <v>6633983</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3102,22 +3100,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3126,13 +3114,9 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3149,7 +3133,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118271746</v>
+        <v>118271860</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -3184,7 +3168,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3192,22 +3176,30 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kivsta, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588381</v>
+        <v>588398</v>
       </c>
       <c r="R21" t="n">
         <v>6633983</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3264,7 +3256,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118271860</v>
+        <v>118253803</v>
       </c>
       <c r="B22" t="n">
         <v>97846</v>
@@ -3309,25 +3301,19 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kivsta, Vstm</t>
+          <t>Överstmossen (Överstmossen), Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588398</v>
+        <v>588370</v>
       </c>
       <c r="R22" t="n">
-        <v>6633983</v>
+        <v>6634068</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3354,12 +3340,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3368,9 +3364,13 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -2899,7 +2899,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118271580</v>
+        <v>118271860</v>
       </c>
       <c r="B19" t="n">
         <v>97846</v>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2942,7 +2942,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
@@ -2955,10 +2959,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588409</v>
+        <v>588398</v>
       </c>
       <c r="R19" t="n">
-        <v>6634007</v>
+        <v>6633983</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3133,7 +3137,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118271860</v>
+        <v>118271580</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -3168,7 +3172,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3176,11 +3180,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588398</v>
+        <v>588409</v>
       </c>
       <c r="R21" t="n">
-        <v>6633983</v>
+        <v>6634007</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3256,7 +3256,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118253803</v>
+        <v>118271652</v>
       </c>
       <c r="B22" t="n">
         <v>97846</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3304,16 +3304,18 @@
           <t>knoppbristning</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Överstmossen (Överstmossen), Vstm</t>
+          <t>Kivsta, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588370</v>
+        <v>588406</v>
       </c>
       <c r="R22" t="n">
-        <v>6634068</v>
+        <v>6634017</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3340,22 +3342,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3364,13 +3356,9 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3387,7 +3375,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118271652</v>
+        <v>118253803</v>
       </c>
       <c r="B23" t="n">
         <v>97846</v>
@@ -3422,7 +3410,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3435,18 +3423,16 @@
           <t>knoppbristning</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kivsta, Vstm</t>
+          <t>Överstmossen (Överstmossen), Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588406</v>
+        <v>588370</v>
       </c>
       <c r="R23" t="n">
-        <v>6634017</v>
+        <v>6634068</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3473,12 +3459,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3487,9 +3483,13 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>121262979</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3757,10 +3757,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121262947</v>
+        <v>121262911</v>
       </c>
       <c r="B26" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3809,14 +3809,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Västerins 2 (knärot), Vstm</t>
+          <t>Vesterins 1 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589031</v>
+        <v>588633</v>
       </c>
       <c r="R26" t="n">
-        <v>6634136</v>
+        <v>6634091</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>U-Sal-1067</t>
+          <t>U-Sal-1066</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (16)</t>
+          <t>minst? X: (5) 20 pl?, A: 509/291(5), 2 pl? i blom foton OK</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3871,11 +3871,6 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>skogsmark</t>
-        </is>
-      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
@@ -3884,7 +3879,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3895,10 +3890,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121262911</v>
+        <v>121263228</v>
       </c>
       <c r="B27" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3930,7 +3925,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3947,17 +3942,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vesterins 1 (knärot), Vstm</t>
+          <t>Västerins 7 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588633</v>
+        <v>588637</v>
       </c>
       <c r="R27" t="n">
-        <v>6634091</v>
+        <v>6634161</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3981,7 +3976,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>U-Sal-1066</t>
+          <t>U-Sal-1073</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3996,7 +3991,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>minst? X: (5) 20 pl?, A: 509/291(5), 2 pl? i blom foton OK</t>
+          <t>foto OK, egentligen (8)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4009,6 +4004,11 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>skogsmark</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4028,10 +4028,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121263228</v>
+        <v>121262947</v>
       </c>
       <c r="B28" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4080,17 +4080,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västerins 7 (knärot), Vstm</t>
+          <t>Västerins 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588637</v>
+        <v>589031</v>
       </c>
       <c r="R28" t="n">
-        <v>6634161</v>
+        <v>6634136</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>U-Sal-1073</t>
+          <t>U-Sal-1067</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (8)</t>
+          <t>foto OK, egentligen (16)</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -3890,7 +3890,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121263228</v>
+        <v>121262947</v>
       </c>
       <c r="B27" t="n">
         <v>98081</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3942,17 +3942,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Västerins 7 (knärot), Vstm</t>
+          <t>Västerins 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588637</v>
+        <v>589031</v>
       </c>
       <c r="R27" t="n">
-        <v>6634161</v>
+        <v>6634136</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>U-Sal-1073</t>
+          <t>U-Sal-1067</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (8)</t>
+          <t>foto OK, egentligen (16)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4028,7 +4028,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121262947</v>
+        <v>121263228</v>
       </c>
       <c r="B28" t="n">
         <v>98081</v>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4080,17 +4080,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västerins 2 (knärot), Vstm</t>
+          <t>Västerins 7 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589031</v>
+        <v>588637</v>
       </c>
       <c r="R28" t="n">
-        <v>6634136</v>
+        <v>6634161</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>U-Sal-1067</t>
+          <t>U-Sal-1073</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (16)</t>
+          <t>foto OK, egentligen (8)</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>121262979</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3757,10 +3757,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121262911</v>
+        <v>121263228</v>
       </c>
       <c r="B26" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3809,17 +3809,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vesterins 1 (knärot), Vstm</t>
+          <t>Västerins 7 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588633</v>
+        <v>588637</v>
       </c>
       <c r="R26" t="n">
-        <v>6634091</v>
+        <v>6634161</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>U-Sal-1066</t>
+          <t>U-Sal-1073</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>minst? X: (5) 20 pl?, A: 509/291(5), 2 pl? i blom foton OK</t>
+          <t>foto OK, egentligen (8)</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3871,6 +3871,11 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>skogsmark</t>
+        </is>
+      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
@@ -3879,7 +3884,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3890,10 +3895,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121262947</v>
+        <v>121262911</v>
       </c>
       <c r="B27" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3925,7 +3930,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3942,14 +3947,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Västerins 2 (knärot), Vstm</t>
+          <t>Vesterins 1 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589031</v>
+        <v>588633</v>
       </c>
       <c r="R27" t="n">
-        <v>6634136</v>
+        <v>6634091</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3976,7 +3981,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>U-Sal-1067</t>
+          <t>U-Sal-1066</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3991,7 +3996,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (16)</t>
+          <t>minst? X: (5) 20 pl?, A: 509/291(5), 2 pl? i blom foton OK</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4004,11 +4009,6 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>skogsmark</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4028,10 +4028,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121263228</v>
+        <v>121262947</v>
       </c>
       <c r="B28" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4080,17 +4080,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västerins 7 (knärot), Vstm</t>
+          <t>Västerins 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588637</v>
+        <v>589031</v>
       </c>
       <c r="R28" t="n">
-        <v>6634161</v>
+        <v>6634136</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>U-Sal-1073</t>
+          <t>U-Sal-1067</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (8)</t>
+          <t>foto OK, egentligen (16)</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>121262979</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>121263228</v>
       </c>
       <c r="B26" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121262911</v>
+        <v>121262947</v>
       </c>
       <c r="B27" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3947,14 +3947,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vesterins 1 (knärot), Vstm</t>
+          <t>Västerins 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588633</v>
+        <v>589031</v>
       </c>
       <c r="R27" t="n">
-        <v>6634091</v>
+        <v>6634136</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>U-Sal-1066</t>
+          <t>U-Sal-1067</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>minst? X: (5) 20 pl?, A: 509/291(5), 2 pl? i blom foton OK</t>
+          <t>foto OK, egentligen (16)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4009,6 +4009,11 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>skogsmark</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -4017,7 +4022,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4028,10 +4033,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121262947</v>
+        <v>121262911</v>
       </c>
       <c r="B28" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4063,7 +4068,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4080,14 +4085,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västerins 2 (knärot), Vstm</t>
+          <t>Vesterins 1 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589031</v>
+        <v>588633</v>
       </c>
       <c r="R28" t="n">
-        <v>6634136</v>
+        <v>6634091</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -4114,7 +4119,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>U-Sal-1067</t>
+          <t>U-Sal-1066</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4129,7 +4134,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (16)</t>
+          <t>minst? X: (5) 20 pl?, A: 509/291(5), 2 pl? i blom foton OK</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4142,11 +4147,6 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>skogsmark</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>121262979</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3757,10 +3757,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121263228</v>
+        <v>121262947</v>
       </c>
       <c r="B26" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3809,17 +3809,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Västerins 7 (knärot), Vstm</t>
+          <t>Västerins 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588637</v>
+        <v>589031</v>
       </c>
       <c r="R26" t="n">
-        <v>6634161</v>
+        <v>6634136</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>U-Sal-1073</t>
+          <t>U-Sal-1067</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (8)</t>
+          <t>foto OK, egentligen (16)</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121262947</v>
+        <v>121263228</v>
       </c>
       <c r="B27" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3947,17 +3947,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Västerins 2 (knärot), Vstm</t>
+          <t>Västerins 7 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589031</v>
+        <v>588637</v>
       </c>
       <c r="R27" t="n">
-        <v>6634136</v>
+        <v>6634161</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>U-Sal-1067</t>
+          <t>U-Sal-1073</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (16)</t>
+          <t>foto OK, egentligen (8)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4036,7 +4036,7 @@
         <v>121262911</v>
       </c>
       <c r="B28" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>121262979</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>121262947</v>
       </c>
       <c r="B26" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>121263228</v>
       </c>
       <c r="B27" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>121262911</v>
       </c>
       <c r="B28" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>121262979</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>121262947</v>
       </c>
       <c r="B26" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>121263228</v>
       </c>
       <c r="B27" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>121262911</v>
       </c>
       <c r="B28" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -3895,7 +3895,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121263228</v>
+        <v>121262911</v>
       </c>
       <c r="B27" t="n">
         <v>98105</v>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3947,17 +3947,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Västerins 7 (knärot), Vstm</t>
+          <t>Vesterins 1 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588637</v>
+        <v>588633</v>
       </c>
       <c r="R27" t="n">
-        <v>6634161</v>
+        <v>6634091</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>U-Sal-1073</t>
+          <t>U-Sal-1066</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (8)</t>
+          <t>minst? X: (5) 20 pl?, A: 509/291(5), 2 pl? i blom foton OK</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4009,11 +4009,6 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>skogsmark</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -4022,7 +4017,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4033,7 +4028,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121262911</v>
+        <v>121263228</v>
       </c>
       <c r="B28" t="n">
         <v>98105</v>
@@ -4068,7 +4063,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4085,17 +4080,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vesterins 1 (knärot), Vstm</t>
+          <t>Västerins 7 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588633</v>
+        <v>588637</v>
       </c>
       <c r="R28" t="n">
-        <v>6634091</v>
+        <v>6634161</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4119,7 +4114,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>U-Sal-1066</t>
+          <t>U-Sal-1073</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4134,7 +4129,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>minst? X: (5) 20 pl?, A: 509/291(5), 2 pl? i blom foton OK</t>
+          <t>foto OK, egentligen (8)</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4147,6 +4142,11 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>skogsmark</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -3757,7 +3757,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121262947</v>
+        <v>121263228</v>
       </c>
       <c r="B26" t="n">
         <v>98105</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3809,17 +3809,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Västerins 2 (knärot), Vstm</t>
+          <t>Västerins 7 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589031</v>
+        <v>588637</v>
       </c>
       <c r="R26" t="n">
-        <v>6634136</v>
+        <v>6634161</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>U-Sal-1067</t>
+          <t>U-Sal-1073</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (16)</t>
+          <t>foto OK, egentligen (8)</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4028,7 +4028,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121263228</v>
+        <v>121262947</v>
       </c>
       <c r="B28" t="n">
         <v>98105</v>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4080,17 +4080,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västerins 7 (knärot), Vstm</t>
+          <t>Västerins 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588637</v>
+        <v>589031</v>
       </c>
       <c r="R28" t="n">
-        <v>6634161</v>
+        <v>6634136</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>U-Sal-1073</t>
+          <t>U-Sal-1067</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (8)</t>
+          <t>foto OK, egentligen (16)</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -3757,7 +3757,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121263228</v>
+        <v>121262947</v>
       </c>
       <c r="B26" t="n">
         <v>98105</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3809,17 +3809,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Västerins 7 (knärot), Vstm</t>
+          <t>Västerins 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588637</v>
+        <v>589031</v>
       </c>
       <c r="R26" t="n">
-        <v>6634161</v>
+        <v>6634136</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>U-Sal-1073</t>
+          <t>U-Sal-1067</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (8)</t>
+          <t>foto OK, egentligen (16)</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3895,7 +3895,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121262911</v>
+        <v>121263228</v>
       </c>
       <c r="B27" t="n">
         <v>98105</v>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3947,17 +3947,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vesterins 1 (knärot), Vstm</t>
+          <t>Västerins 7 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588633</v>
+        <v>588637</v>
       </c>
       <c r="R27" t="n">
-        <v>6634091</v>
+        <v>6634161</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>U-Sal-1066</t>
+          <t>U-Sal-1073</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>minst? X: (5) 20 pl?, A: 509/291(5), 2 pl? i blom foton OK</t>
+          <t>foto OK, egentligen (8)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4009,6 +4009,11 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>skogsmark</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -4017,7 +4022,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Thomé</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4028,7 +4033,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121262947</v>
+        <v>121262911</v>
       </c>
       <c r="B28" t="n">
         <v>98105</v>
@@ -4063,7 +4068,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4080,14 +4085,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västerins 2 (knärot), Vstm</t>
+          <t>Vesterins 1 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589031</v>
+        <v>588633</v>
       </c>
       <c r="R28" t="n">
-        <v>6634136</v>
+        <v>6634091</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -4114,7 +4119,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>U-Sal-1067</t>
+          <t>U-Sal-1066</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4129,7 +4134,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>foto OK, egentligen (16)</t>
+          <t>minst? X: (5) 20 pl?, A: 509/291(5), 2 pl? i blom foton OK</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4142,11 +4147,6 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>skogsmark</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Maria Thomé</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1721,11 +1721,11 @@
         <v>118260266</v>
       </c>
       <c r="B10" t="n">
-        <v>57306</v>
+        <v>57381</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Överstmossen (Överstmossen), Vstm</t>
+          <t>Överstmossen, Överstmossen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1721,7 +1721,7 @@
         <v>118260266</v>
       </c>
       <c r="B10" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1721,7 +1721,7 @@
         <v>118260266</v>
       </c>
       <c r="B10" t="n">
-        <v>57385</v>
+        <v>57388</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1721,7 +1721,7 @@
         <v>118260266</v>
       </c>
       <c r="B10" t="n">
-        <v>57388</v>
+        <v>57390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1721,7 +1721,7 @@
         <v>118260266</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1736,11 +1736,6 @@
       <c r="E10" t="n">
         <v>100049</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1818,11 +1813,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">

--- a/artfynd/A 23221-2023 artfynd.xlsx
+++ b/artfynd/A 23221-2023 artfynd.xlsx
@@ -1721,7 +1721,7 @@
         <v>118260266</v>
       </c>
       <c r="B10" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,6 +1736,11 @@
       <c r="E10" t="n">
         <v>100049</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1813,6 +1818,11 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
